--- a/survey_templates/038_employee_engagement_survey--survey_templates.xlsx
+++ b/survey_templates/038_employee_engagement_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -949,8 +949,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,12 +978,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small',_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small', 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large',_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large', 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_1_year',_'label':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Less than 1 year', 'label': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'1-2_years',_'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '1-2 years', 'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'2-5_years',_'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '2-5 years', 'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'5-10_years',_'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '5-10 years', 'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'more_than_10_years',_'label':_'more_than_10_years'}</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'More than 10 years', 'label': 'More than 10 years'}</t>
+          <t>More than 10 years</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'very_poor',_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Very Poor', 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Very Good', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Very Good', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'Fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'very_fair',_'label':_'very_fair'}</t>
+          <t>very_fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Very Fair', 'label': 'Very Fair'}</t>
+          <t>Very Fair</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'very_important',_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Very Important', 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Somewhat Important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'not_very_important',_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Not Very Important', 'label': 'Not Very Important'}</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Very Good', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'Fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'very_fair',_'label':_'very_fair'}</t>
+          <t>very_fair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'Very Fair', 'label': 'Very Fair'}</t>
+          <t>Very Fair</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'very_important',_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'Very Important', 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'somewhat_important',_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'Somewhat Important', 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'not_very_important',_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'Not Very Important', 'label': 'Not Very Important'}</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
